--- a/assets/templates/Lista_de_Precios_y_Cantidades.xlsx
+++ b/assets/templates/Lista_de_Precios_y_Cantidades.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LEEME" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISTA_PRECIOS_CANT'!$A$1:$E$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'LISTA_PRECIOS_CANT'!$A$1:$K$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -221,12 +221,42 @@
     </comment>
     <comment ref="D1" authorId="0" shapeId="0">
       <text>
-        <t>Descuento 1 (fracción, ej: 0.05 = 5%) — opcional</t>
+        <t>Primer descuento en % (fracción: 0.05 = 5%) — cascada</t>
       </text>
     </comment>
     <comment ref="E1" authorId="0" shapeId="0">
       <text>
-        <t>Descuento 2 (fracción) — opcional</t>
+        <t>Segundo descuento en % (fracción) — cascada</t>
+      </text>
+    </comment>
+    <comment ref="F1" authorId="0" shapeId="0">
+      <text>
+        <t>Tercer descuento en % (fracción) — cascada</t>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0">
+      <text>
+        <t>Cuarto descuento en % (fracción) — cascada</t>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="0" shapeId="0">
+      <text>
+        <t>Quinto descuento en % (fracción) — cascada</t>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="0" shapeId="0">
+      <text>
+        <t>Sexto descuento en % (fracción) — cascada</t>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="0" shapeId="0">
+      <text>
+        <t>Séptimo descuento en % (fracción) — cascada</t>
+      </text>
+    </comment>
+    <comment ref="K1" authorId="0" shapeId="0">
+      <text>
+        <t>Octavo descuento en % (fracción) — cascada</t>
       </text>
     </comment>
   </commentList>
@@ -522,7 +552,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -530,6 +560,12 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="18" customWidth="1" min="4" max="4"/>
     <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -558,6 +594,36 @@
           <t>DESC02</t>
         </is>
       </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>DESC03</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>DESC04</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>DESC05</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>DESC06</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>DESC07</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>DESC08</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
@@ -575,6 +641,24 @@
         <v>0.05</v>
       </c>
       <c r="E2" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F2" s="8" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="G2" s="8" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="H2" s="8" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J2" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K2" s="8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -591,10 +675,28 @@
         <v>4.8</v>
       </c>
       <c r="D3" s="8" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>0.05</v>
+        <v>0</v>
+      </c>
+      <c r="F3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J3" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="K3" s="8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="4">
@@ -611,9 +713,15 @@
       </c>
       <c r="D4" s="8" t="n"/>
       <c r="E4" s="8" t="n"/>
+      <c r="F4" s="8" t="n"/>
+      <c r="G4" s="8" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
+      <c r="J4" s="8" t="n"/>
+      <c r="K4" s="8" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E1"/>
+  <autoFilter ref="A1:K1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
@@ -641,7 +749,7 @@
     <row r="2">
       <c r="A2" s="10" t="inlineStr">
         <is>
-          <t>Precio de lista y cantidad a reconocer por SKU (VRS).</t>
+          <t>Precio de lista y cantidad a reconocer por SKU (VRS). La cadena de descuentos se aplica en cascada: PRECIO_BASE × (1−DESC01) × (1−DESC02) × … × (1−DESC08).</t>
         </is>
       </c>
     </row>
